--- a/docs/sample-outputs/report_lesson_logs_messy.xlsx
+++ b/docs/sample-outputs/report_lesson_logs_messy.xlsx
@@ -14,7 +14,34 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="83">
+  <si>
+    <t>NULL_FIELD</t>
+  </si>
+  <si>
+    <t>INVALID_VALUE</t>
+  </si>
+  <si>
+    <t>NULL_RECORD</t>
+  </si>
+  <si>
+    <t>REFERENCE_NOT_FOUND</t>
+  </si>
+  <si>
+    <t>Row 4 is missing mandatory data in field(s): Fees Charged.</t>
+  </si>
+  <si>
+    <t>Row 4 has an invalid non-numeric value in 'Fees Charged': 'TBC'.</t>
+  </si>
+  <si>
+    <t>Row 6 is completely empty.</t>
+  </si>
+  <si>
+    <t>Row 11 is completely empty.</t>
+  </si>
+  <si>
+    <t>Assignment ID 'TAS-009' not found. File could not be saved to database.</t>
+  </si>
   <si>
     <t>LOG-001</t>
   </si>
@@ -115,7 +142,7 @@
     <t>2025-04-26</t>
   </si>
   <si>
-    <t>03/06/25</t>
+    <t>2025-06-03</t>
   </si>
   <si>
     <t>2025-07-09</t>
@@ -130,7 +157,7 @@
     <t>2025-01-15</t>
   </si>
   <si>
-    <t>05/09/25</t>
+    <t>2025-09-05</t>
   </si>
   <si>
     <t>2025-03-19</t>
@@ -208,31 +235,13 @@
     <t>TBC</t>
   </si>
   <si>
-    <t>MISSING_RELATIONSHIP</t>
-  </si>
-  <si>
-    <t>NULL_RECORD</t>
-  </si>
-  <si>
-    <t>NULL_FIELD</t>
-  </si>
-  <si>
-    <t>Assignment ID 'TAS-004' not found. File could not be saved to database.</t>
-  </si>
-  <si>
-    <t>Row 6 is completely empty.</t>
-  </si>
-  <si>
-    <t>Assignment ID 'TAS-007' not found. File could not be saved to database.</t>
-  </si>
-  <si>
-    <t>Row 11 is completely empty.</t>
-  </si>
-  <si>
-    <t>Row 14 is missing mandatory data in: Duration (Hours).</t>
-  </si>
-  <si>
-    <t>Assignment ID 'TAS-009' not found. File could not be saved to database.</t>
+    <t>Row Index</t>
+  </si>
+  <si>
+    <t>Reason Code</t>
+  </si>
+  <si>
+    <t>Error Details</t>
   </si>
   <si>
     <t>Log ID</t>
@@ -254,12 +263,6 @@
   </si>
   <si>
     <t>Fees Charged</t>
-  </si>
-  <si>
-    <t>Reason Code</t>
-  </si>
-  <si>
-    <t>Error Details</t>
   </si>
 </sst>
 </file>
@@ -629,21 +632,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" customWidth="1"/>
-    <col min="6" max="6" width="33.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" customWidth="1"/>
-    <col min="9" max="9" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="33.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>73</v>
       </c>
@@ -671,410 +675,490 @@
       <c r="I1" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="J1" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J2" s="2">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J4" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="2">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="D11" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="1">
+      <c r="F12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2</v>
+      </c>
+      <c r="H12" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14" s="1">
         <v>1.5</v>
       </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="H14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="2">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>54</v>
+      </c>
+      <c r="I15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="2">
+        <v>82.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="2">
-        <v>82.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
+      <c r="G16" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="H16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="D17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="1">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" t="s">
+        <v>68</v>
+      </c>
+      <c r="J17" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J18" s="2">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G19" s="1">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="2">
+      <c r="H19" t="s">
+        <v>55</v>
+      </c>
+      <c r="I19" t="s">
+        <v>70</v>
+      </c>
+      <c r="J19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" t="s">
+        <v>71</v>
+      </c>
+      <c r="J20" s="2">
         <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G4" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="2">
-        <v>82.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="H7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="2">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="H12" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="2">
-        <v>82.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="E14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G14" s="2">
-        <v>82.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="2">
-        <v>60</v>
-      </c>
-      <c r="H15" t="s">
-        <v>66</v>
-      </c>
-      <c r="I15" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="E17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" s="2">
-        <v>67.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>46</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="2">
-        <v>45</v>
-      </c>
-      <c r="H19" t="s">
-        <v>64</v>
-      </c>
-      <c r="I19" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
